--- a/wk4/PivotTable_tutorial.xlsx
+++ b/wk4/PivotTable_tutorial.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD0043BF-DE1B-4932-AC01-51A062B3411B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <workbookPr filterPrivacy="1" codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1C9E50-04F3-4B42-B2C3-EF5F73C6E547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="910" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-37640" yWindow="-4580" windowWidth="29400" windowHeight="17160" tabRatio="910" firstSheet="6" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="2" r:id="rId1"/>
@@ -36,17 +36,17 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="11" r:id="rId23"/>
-    <pivotCache cacheId="12" r:id="rId24"/>
-    <pivotCache cacheId="13" r:id="rId25"/>
-    <pivotCache cacheId="14" r:id="rId26"/>
-    <pivotCache cacheId="15" r:id="rId27"/>
-    <pivotCache cacheId="16" r:id="rId28"/>
-    <pivotCache cacheId="17" r:id="rId29"/>
-    <pivotCache cacheId="18" r:id="rId30"/>
-    <pivotCache cacheId="19" r:id="rId31"/>
-    <pivotCache cacheId="24" r:id="rId32"/>
-    <pivotCache cacheId="21" r:id="rId33"/>
+    <pivotCache cacheId="0" r:id="rId23"/>
+    <pivotCache cacheId="1" r:id="rId24"/>
+    <pivotCache cacheId="2" r:id="rId25"/>
+    <pivotCache cacheId="3" r:id="rId26"/>
+    <pivotCache cacheId="4" r:id="rId27"/>
+    <pivotCache cacheId="5" r:id="rId28"/>
+    <pivotCache cacheId="18" r:id="rId29"/>
+    <pivotCache cacheId="17" r:id="rId30"/>
+    <pivotCache cacheId="8" r:id="rId31"/>
+    <pivotCache cacheId="16" r:id="rId32"/>
+    <pivotCache cacheId="15" r:id="rId33"/>
   </pivotCaches>
   <fileRecoveryPr autoRecover="0"/>
   <extLst>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="96">
   <si>
     <t>Go back to top by pressing CTRL+HOME. To start the tour, press CTRL+PAGE DOWN.</t>
   </si>
@@ -296,9 +296,6 @@
     <t>Cells H10 through I17 contain a PivotTable which summarizes the data. The PivotTable has two columns: Type and Sum of Amount. The Type column contains the values Books, Food, Fuel, Music, Sports, Tickets, and Grand Total; the Sum of Amount column contains the values $125, $470, $74, $20, $20, $125, and $834. There is a label pointing to the Type column that says, "We added a condition here to divide the value field by 'Type.'" There is also a label that points to the Sum of Amount column that says, "Value field."</t>
   </si>
   <si>
-    <t xml:space="preserve">When you create a PivotTable in a moment, you'll see the PivotTable Fields List. It's not just a list though, it's a more like a panel. At the top you'll see the fields from your data. </t>
-  </si>
-  <si>
     <t>A PivotTable Fields List image shows an arrow cursor dragging the Amount field to the Values area.</t>
   </si>
   <si>
@@ -380,6 +377,12 @@
   </si>
   <si>
     <t xml:space="preserve">Then you'll want a condition to divide the value field by. And to do that, you drag any of the other fields down to the Rows area. </t>
+  </si>
+  <si>
+    <t>Buyers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mm </t>
   </si>
 </sst>
 </file>
@@ -791,7 +794,68 @@
     <cellStyle name="Title" xfId="2" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
     <cellStyle name="z A Column text" xfId="5" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
   </cellStyles>
-  <dxfs count="113">
+  <dxfs count="116">
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="65"/>
+          <bgColor theme="7" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="65"/>
+          <bgColor theme="7" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="9" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="9" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1502,58 +1566,6 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="9" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="65"/>
-          <bgColor theme="7" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="65"/>
-          <bgColor theme="7" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -2211,186 +2223,6 @@
           <bgColor theme="9"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="9" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9" tint="0.79998168889431442"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9" tint="0.79998168889431442"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9" tint="0.79998168889431442"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="dd\-mmm"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9" tint="0.79998168889431442"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="9" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
@@ -3439,6 +3271,186 @@
     <dxf>
       <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="9" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="dd\-mmm"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="9" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium7" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -5572,8 +5584,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5668328" y="1163955"/>
-          <a:ext cx="913447" cy="667113"/>
+          <a:off x="6275388" y="1209675"/>
+          <a:ext cx="913447" cy="697593"/>
           <a:chOff x="5756275" y="1171575"/>
           <a:chExt cx="930275" cy="672193"/>
         </a:xfrm>
@@ -5716,8 +5728,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2183130" y="1163955"/>
-          <a:ext cx="2966451" cy="937945"/>
+          <a:off x="2381250" y="1209675"/>
+          <a:ext cx="3289031" cy="976045"/>
           <a:chOff x="2209800" y="1171575"/>
           <a:chExt cx="3022331" cy="944295"/>
         </a:xfrm>
@@ -6664,8 +6676,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5620703" y="971550"/>
-          <a:ext cx="961072" cy="668383"/>
+          <a:off x="6227763" y="1009650"/>
+          <a:ext cx="961072" cy="691243"/>
           <a:chOff x="5708650" y="977900"/>
           <a:chExt cx="942975" cy="672193"/>
         </a:xfrm>
@@ -6808,8 +6820,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2135505" y="971550"/>
-          <a:ext cx="2966451" cy="937945"/>
+          <a:off x="2333625" y="1009650"/>
+          <a:ext cx="3289031" cy="976045"/>
           <a:chOff x="2162175" y="977900"/>
           <a:chExt cx="3022331" cy="944295"/>
         </a:xfrm>
@@ -7832,8 +7844,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5887403" y="1192530"/>
-          <a:ext cx="913447" cy="458833"/>
+          <a:off x="6481763" y="1238250"/>
+          <a:ext cx="1017587" cy="481693"/>
           <a:chOff x="5975350" y="1200150"/>
           <a:chExt cx="930275" cy="462643"/>
         </a:xfrm>
@@ -7976,8 +7988,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4672965" y="1192530"/>
-          <a:ext cx="957263" cy="458833"/>
+          <a:off x="5076825" y="1238250"/>
+          <a:ext cx="1147763" cy="481693"/>
           <a:chOff x="4733925" y="1200150"/>
           <a:chExt cx="984250" cy="462643"/>
         </a:xfrm>
@@ -9008,8 +9020,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="647113" y="1147172"/>
-          <a:ext cx="2544350" cy="501016"/>
+          <a:off x="713153" y="1192892"/>
+          <a:ext cx="2742470" cy="523876"/>
           <a:chOff x="656003" y="1154792"/>
           <a:chExt cx="2571020" cy="504826"/>
         </a:xfrm>
@@ -9147,8 +9159,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6106478" y="1135380"/>
-          <a:ext cx="913447" cy="466453"/>
+          <a:off x="6700838" y="1181100"/>
+          <a:ext cx="1017587" cy="481693"/>
           <a:chOff x="6194425" y="1143000"/>
           <a:chExt cx="930275" cy="468993"/>
         </a:xfrm>
@@ -9309,8 +9321,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4234816" y="1135380"/>
-          <a:ext cx="1738312" cy="466453"/>
+          <a:off x="4638676" y="1181100"/>
+          <a:ext cx="1928812" cy="481693"/>
           <a:chOff x="4295776" y="1143000"/>
           <a:chExt cx="1765299" cy="468993"/>
         </a:xfrm>
@@ -10405,8 +10417,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2876002" y="1624965"/>
-          <a:ext cx="2538374" cy="1339190"/>
+          <a:off x="3160482" y="1685925"/>
+          <a:ext cx="2871114" cy="1400150"/>
           <a:chOff x="2792182" y="1685925"/>
           <a:chExt cx="2467889" cy="1400150"/>
         </a:xfrm>
@@ -10608,8 +10620,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="266700" y="1615441"/>
-          <a:ext cx="1863091" cy="1031924"/>
+          <a:off x="266700" y="1676401"/>
+          <a:ext cx="2076451" cy="1077644"/>
           <a:chOff x="266700" y="1625601"/>
           <a:chExt cx="1885951" cy="1039544"/>
         </a:xfrm>
@@ -11640,8 +11652,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1068379" y="1798319"/>
-          <a:ext cx="3106111" cy="2223135"/>
+          <a:off x="1139499" y="1854199"/>
+          <a:ext cx="3464251" cy="2314575"/>
           <a:chOff x="1075999" y="1809749"/>
           <a:chExt cx="3153101" cy="2238375"/>
         </a:xfrm>
@@ -12767,8 +12779,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1203960" y="1280160"/>
-          <a:ext cx="2688907" cy="696958"/>
+          <a:off x="1346200" y="1333500"/>
+          <a:ext cx="2935287" cy="719818"/>
           <a:chOff x="1219200" y="1289050"/>
           <a:chExt cx="2720975" cy="700768"/>
         </a:xfrm>
@@ -14557,8 +14569,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2444115" y="1365885"/>
-          <a:ext cx="1524952" cy="620758"/>
+          <a:off x="2657475" y="1419225"/>
+          <a:ext cx="1730692" cy="643618"/>
           <a:chOff x="2466975" y="1374775"/>
           <a:chExt cx="1546224" cy="624568"/>
         </a:xfrm>
@@ -14734,8 +14746,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="849629" y="1356360"/>
-          <a:ext cx="1451609" cy="630283"/>
+          <a:off x="920749" y="1409700"/>
+          <a:ext cx="1593849" cy="653143"/>
           <a:chOff x="857249" y="1365250"/>
           <a:chExt cx="1466849" cy="634093"/>
         </a:xfrm>
@@ -15618,8 +15630,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="76200" y="593090"/>
-          <a:ext cx="1884681" cy="1369060"/>
+          <a:off x="76200" y="615950"/>
+          <a:ext cx="2082801" cy="1422400"/>
           <a:chOff x="76200" y="596900"/>
           <a:chExt cx="1911351" cy="1377950"/>
         </a:xfrm>
@@ -16020,8 +16032,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2064597" y="593090"/>
-          <a:ext cx="1851661" cy="1723389"/>
+          <a:off x="2262717" y="615950"/>
+          <a:ext cx="2057401" cy="1797049"/>
           <a:chOff x="2091267" y="596900"/>
           <a:chExt cx="1885951" cy="1737815"/>
         </a:xfrm>
@@ -16462,8 +16474,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6195695" y="596265"/>
-          <a:ext cx="1900555" cy="1365885"/>
+          <a:off x="6830695" y="619125"/>
+          <a:ext cx="2131695" cy="1419225"/>
           <a:chOff x="6296025" y="600075"/>
           <a:chExt cx="1939925" cy="1374775"/>
         </a:xfrm>
@@ -16904,8 +16916,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4003040" y="596265"/>
-          <a:ext cx="2100580" cy="855346"/>
+          <a:off x="4406900" y="619125"/>
+          <a:ext cx="2331720" cy="885826"/>
           <a:chOff x="4064000" y="600075"/>
           <a:chExt cx="2139950" cy="860426"/>
         </a:xfrm>
@@ -18166,8 +18178,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="688340" y="1003322"/>
-          <a:ext cx="2524125" cy="561318"/>
+          <a:off x="754380" y="1041422"/>
+          <a:ext cx="2722245" cy="584178"/>
           <a:chOff x="697230" y="1009672"/>
           <a:chExt cx="2560320" cy="565128"/>
         </a:xfrm>
@@ -18315,8 +18327,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3930017" y="990621"/>
-          <a:ext cx="2846069" cy="624825"/>
+          <a:off x="4333877" y="1028721"/>
+          <a:ext cx="3155949" cy="647685"/>
           <a:chOff x="3986515" y="997256"/>
           <a:chExt cx="2909654" cy="628351"/>
         </a:xfrm>
@@ -19216,8 +19228,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="821055" y="4683125"/>
-          <a:ext cx="6402705" cy="1207135"/>
+          <a:off x="892175" y="4873625"/>
+          <a:ext cx="7134225" cy="1260475"/>
           <a:chOff x="828675" y="4714875"/>
           <a:chExt cx="6511925" cy="1216025"/>
         </a:xfrm>
@@ -19680,8 +19692,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4962525" y="2094230"/>
-          <a:ext cx="1640205" cy="2371090"/>
+          <a:off x="5508625" y="2178050"/>
+          <a:ext cx="1825625" cy="2470150"/>
           <a:chOff x="5038725" y="2108200"/>
           <a:chExt cx="1673225" cy="2387600"/>
         </a:xfrm>
@@ -20547,8 +20559,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="76200" y="596265"/>
-          <a:ext cx="1887856" cy="1365885"/>
+          <a:off x="76200" y="619125"/>
+          <a:ext cx="2085976" cy="1419225"/>
           <a:chOff x="76200" y="600075"/>
           <a:chExt cx="1914526" cy="1374775"/>
         </a:xfrm>
@@ -20909,8 +20921,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2156672" y="596265"/>
-          <a:ext cx="1851661" cy="1885950"/>
+          <a:off x="2354792" y="619125"/>
+          <a:ext cx="2057401" cy="1962150"/>
           <a:chOff x="2183342" y="600075"/>
           <a:chExt cx="1885951" cy="1570445"/>
         </a:xfrm>
@@ -21448,8 +21460,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5883275" y="596265"/>
-          <a:ext cx="1821181" cy="1895474"/>
+          <a:off x="6480175" y="619125"/>
+          <a:ext cx="1993901" cy="1971674"/>
           <a:chOff x="5978525" y="600075"/>
           <a:chExt cx="1847851" cy="1908174"/>
         </a:xfrm>
@@ -21850,8 +21862,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4060189" y="593090"/>
-          <a:ext cx="1784987" cy="1369060"/>
+          <a:off x="4464049" y="615950"/>
+          <a:ext cx="1978027" cy="1422400"/>
           <a:chOff x="4121149" y="596900"/>
           <a:chExt cx="1819277" cy="1377950"/>
         </a:xfrm>
@@ -23077,8 +23089,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2736894" y="2308860"/>
-          <a:ext cx="633576" cy="316691"/>
+          <a:off x="2808014" y="2247900"/>
+          <a:ext cx="633576" cy="306531"/>
           <a:chOff x="10096500" y="4114799"/>
           <a:chExt cx="914400" cy="476251"/>
         </a:xfrm>
@@ -24355,8 +24367,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3867151" y="997607"/>
-          <a:ext cx="3289125" cy="602600"/>
+          <a:off x="4282441" y="1049042"/>
+          <a:ext cx="3647900" cy="627365"/>
           <a:chOff x="3933826" y="1009672"/>
           <a:chExt cx="3381835" cy="615935"/>
         </a:xfrm>
@@ -25260,8 +25272,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3688079" y="961413"/>
-          <a:ext cx="3557415" cy="638794"/>
+          <a:off x="4035424" y="1012848"/>
+          <a:ext cx="4018425" cy="663559"/>
           <a:chOff x="3749674" y="981955"/>
           <a:chExt cx="3661237" cy="643652"/>
         </a:xfrm>
@@ -26199,8 +26211,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="651509" y="1000147"/>
-          <a:ext cx="2535555" cy="615299"/>
+          <a:off x="717549" y="1038247"/>
+          <a:ext cx="2733675" cy="638159"/>
           <a:chOff x="660399" y="1006497"/>
           <a:chExt cx="2562225" cy="619109"/>
         </a:xfrm>
@@ -26348,8 +26360,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3316602" y="1655450"/>
-          <a:ext cx="2545718" cy="1451605"/>
+          <a:off x="3654422" y="1724030"/>
+          <a:ext cx="2759078" cy="1504945"/>
           <a:chOff x="3368672" y="1666880"/>
           <a:chExt cx="2581278" cy="1460495"/>
         </a:xfrm>
@@ -27310,8 +27322,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="656616" y="1116330"/>
-          <a:ext cx="548914" cy="530830"/>
+          <a:off x="722656" y="1162050"/>
+          <a:ext cx="548914" cy="553690"/>
           <a:chOff x="665506" y="1123950"/>
           <a:chExt cx="548914" cy="534640"/>
         </a:xfrm>
@@ -27465,8 +27477,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1229438" y="1116948"/>
-          <a:ext cx="674367" cy="529592"/>
+          <a:off x="1295478" y="1162668"/>
+          <a:ext cx="806447" cy="552452"/>
           <a:chOff x="1238328" y="1124568"/>
           <a:chExt cx="692147" cy="533402"/>
         </a:xfrm>
@@ -27620,8 +27632,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1933931" y="1116948"/>
-          <a:ext cx="619757" cy="529592"/>
+          <a:off x="2132051" y="1162668"/>
+          <a:ext cx="685797" cy="552452"/>
           <a:chOff x="1960601" y="1124568"/>
           <a:chExt cx="628647" cy="533402"/>
         </a:xfrm>
@@ -27775,8 +27787,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2583816" y="1116948"/>
-          <a:ext cx="600072" cy="529592"/>
+          <a:off x="2847976" y="1162668"/>
+          <a:ext cx="600072" cy="552452"/>
           <a:chOff x="2619376" y="1124568"/>
           <a:chExt cx="600072" cy="533402"/>
         </a:xfrm>
@@ -27930,8 +27942,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3987165" y="1289685"/>
-          <a:ext cx="3143250" cy="1817370"/>
+          <a:off x="4391025" y="1343025"/>
+          <a:ext cx="3473450" cy="1885950"/>
           <a:chOff x="4048125" y="1298575"/>
           <a:chExt cx="3200400" cy="1828800"/>
         </a:xfrm>
@@ -28987,8 +28999,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2882265" y="1073150"/>
-          <a:ext cx="2773681" cy="810880"/>
+          <a:off x="3146425" y="1111250"/>
+          <a:ext cx="3060701" cy="848980"/>
           <a:chOff x="2917825" y="1079500"/>
           <a:chExt cx="2825751" cy="817230"/>
         </a:xfrm>
@@ -29124,8 +29136,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>604457</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>185357</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>33528</xdr:rowOff>
     </xdr:to>
@@ -29489,8 +29501,8 @@
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>604457</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>185357</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -29655,13 +29667,13 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>453327</xdr:colOff>
+      <xdr:colOff>567627</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>59326</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>79693</xdr:colOff>
+      <xdr:colOff>333693</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>35925</xdr:rowOff>
     </xdr:to>
@@ -30009,7 +30021,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>353042</xdr:colOff>
+      <xdr:colOff>607042</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>2</xdr:rowOff>
     </xdr:to>
@@ -30026,8 +30038,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3676651" y="1035684"/>
-          <a:ext cx="3450571" cy="593093"/>
+          <a:off x="4025901" y="1079499"/>
+          <a:ext cx="3870941" cy="635003"/>
           <a:chOff x="3740151" y="1047749"/>
           <a:chExt cx="3529628" cy="609603"/>
         </a:xfrm>
@@ -30161,8 +30173,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>547307</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>102807</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>33528</xdr:rowOff>
     </xdr:to>
@@ -30450,8 +30462,8 @@
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>547307</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>102807</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -30616,13 +30628,13 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>430594</xdr:colOff>
+      <xdr:colOff>544894</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>59326</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>25210</xdr:colOff>
+      <xdr:colOff>279210</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>35925</xdr:rowOff>
     </xdr:to>
@@ -30987,8 +30999,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="680085" y="1116330"/>
-          <a:ext cx="2827020" cy="696958"/>
+          <a:off x="746125" y="1162050"/>
+          <a:ext cx="3098800" cy="719818"/>
           <a:chOff x="688975" y="1123950"/>
           <a:chExt cx="2870200" cy="700768"/>
         </a:xfrm>
@@ -31114,7 +31126,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>433388</xdr:colOff>
+      <xdr:colOff>687388</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>167368</xdr:rowOff>
     </xdr:to>
@@ -31131,8 +31143,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4501515" y="1116330"/>
-          <a:ext cx="2759393" cy="696958"/>
+          <a:off x="4905375" y="1162050"/>
+          <a:ext cx="3097213" cy="719818"/>
           <a:chOff x="4562475" y="1123950"/>
           <a:chExt cx="2819400" cy="700768"/>
         </a:xfrm>
@@ -31321,6 +31333,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
       <x14:pivotCacheDefinition/>
     </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
+    </ext>
   </extLst>
 </pivotCacheDefinition>
 </file>
@@ -31359,6 +31374,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
       <x14:pivotCacheDefinition/>
     </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
+    </ext>
   </extLst>
 </pivotCacheDefinition>
 </file>
@@ -31370,7 +31388,15 @@
   </cacheSource>
   <cacheFields count="4">
     <cacheField name="Date" numFmtId="164">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2017-01-01T00:00:00" maxDate="2017-02-26T00:00:00"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2017-01-01T00:00:00" maxDate="2017-02-26T00:00:00" count="7">
+        <d v="2017-01-01T00:00:00"/>
+        <d v="2017-01-15T00:00:00"/>
+        <d v="2017-01-17T00:00:00"/>
+        <d v="2017-01-21T00:00:00"/>
+        <d v="2017-02-02T00:00:00"/>
+        <d v="2017-02-20T00:00:00"/>
+        <d v="2017-02-25T00:00:00"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Buyer" numFmtId="0">
       <sharedItems count="3">
@@ -31380,15 +31406,30 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Type" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="6">
+        <s v="Fuel"/>
+        <s v="Food"/>
+        <s v="Sports"/>
+        <s v="Books"/>
+        <s v="Music"/>
+        <s v="Tickets"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Amount" numFmtId="5">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="20" maxValue="235"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="20" maxValue="235" count="4">
+        <n v="74"/>
+        <n v="235"/>
+        <n v="20"/>
+        <n v="125"/>
+      </sharedItems>
     </cacheField>
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
       <x14:pivotCacheDefinition/>
+    </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -31824,6 +31865,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
       <x14:pivotCacheDefinition/>
     </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
+    </ext>
   </extLst>
 </pivotCacheDefinition>
 </file>
@@ -31855,6 +31899,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
       <x14:pivotCacheDefinition/>
     </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
+    </ext>
   </extLst>
 </pivotCacheDefinition>
 </file>
@@ -31885,6 +31932,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
       <x14:pivotCacheDefinition/>
+    </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -31924,6 +31974,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
       <x14:pivotCacheDefinition/>
     </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
+    </ext>
   </extLst>
 </pivotCacheDefinition>
 </file>
@@ -31962,6 +32015,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
       <x14:pivotCacheDefinition/>
     </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
+    </ext>
   </extLst>
 </pivotCacheDefinition>
 </file>
@@ -31979,7 +32035,14 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="Type" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="6">
+        <s v="Fuel"/>
+        <s v="Food"/>
+        <s v="Sports"/>
+        <s v="Books"/>
+        <s v="Music"/>
+        <s v="Tickets"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Amount" numFmtId="5">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="20" maxValue="235"/>
@@ -31988,6 +32051,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
       <x14:pivotCacheDefinition/>
+    </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -32003,7 +32069,11 @@
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2017-01-01T00:00:00" maxDate="2017-02-26T00:00:00"/>
     </cacheField>
     <cacheField name="Buyer" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="3">
+        <s v="Mom"/>
+        <s v="Dad"/>
+        <s v="Kelly"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Type" numFmtId="0">
       <sharedItems/>
@@ -32015,6 +32085,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
       <x14:pivotCacheDefinition/>
+    </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -32053,6 +32126,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
       <x14:pivotCacheDefinition/>
+    </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -32155,46 +32231,46 @@
 <file path=xl/pivotCache/pivotCacheRecords11.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="7">
   <r>
-    <d v="2017-01-01T00:00:00"/>
     <x v="0"/>
-    <s v="Fuel"/>
-    <n v="74"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
-    <d v="2017-01-15T00:00:00"/>
+    <x v="1"/>
     <x v="0"/>
-    <s v="Food"/>
-    <n v="235"/>
+    <x v="1"/>
+    <x v="1"/>
   </r>
   <r>
-    <d v="2017-01-17T00:00:00"/>
+    <x v="2"/>
     <x v="1"/>
-    <s v="Sports"/>
-    <n v="20"/>
+    <x v="2"/>
+    <x v="2"/>
   </r>
   <r>
-    <d v="2017-01-21T00:00:00"/>
+    <x v="3"/>
     <x v="2"/>
-    <s v="Books"/>
-    <n v="125"/>
+    <x v="3"/>
+    <x v="3"/>
   </r>
   <r>
-    <d v="2017-02-02T00:00:00"/>
+    <x v="4"/>
     <x v="0"/>
-    <s v="Food"/>
-    <n v="235"/>
+    <x v="1"/>
+    <x v="1"/>
   </r>
   <r>
-    <d v="2017-02-20T00:00:00"/>
+    <x v="5"/>
     <x v="2"/>
-    <s v="Music"/>
-    <n v="20"/>
+    <x v="4"/>
+    <x v="2"/>
   </r>
   <r>
-    <d v="2017-02-25T00:00:00"/>
+    <x v="6"/>
     <x v="2"/>
-    <s v="Tickets"/>
-    <n v="125"/>
+    <x v="5"/>
+    <x v="3"/>
   </r>
 </pivotCacheRecords>
 </file>
@@ -32439,43 +32515,43 @@
   <r>
     <d v="2017-01-01T00:00:00"/>
     <s v="Mom"/>
-    <s v="Fuel"/>
+    <x v="0"/>
     <n v="74"/>
   </r>
   <r>
     <d v="2017-01-15T00:00:00"/>
     <s v="Mom"/>
-    <s v="Food"/>
+    <x v="1"/>
     <n v="235"/>
   </r>
   <r>
     <d v="2017-01-17T00:00:00"/>
     <s v="Dad"/>
-    <s v="Sports"/>
+    <x v="2"/>
     <n v="20"/>
   </r>
   <r>
     <d v="2017-01-21T00:00:00"/>
     <s v="Kelly"/>
-    <s v="Books"/>
+    <x v="3"/>
     <n v="125"/>
   </r>
   <r>
     <d v="2017-02-02T00:00:00"/>
     <s v="Mom"/>
-    <s v="Food"/>
+    <x v="1"/>
     <n v="235"/>
   </r>
   <r>
     <d v="2017-02-20T00:00:00"/>
     <s v="Kelly"/>
-    <s v="Music"/>
+    <x v="4"/>
     <n v="20"/>
   </r>
   <r>
     <d v="2017-02-25T00:00:00"/>
     <s v="Kelly"/>
-    <s v="Tickets"/>
+    <x v="5"/>
     <n v="125"/>
   </r>
 </pivotCacheRecords>
@@ -32485,43 +32561,43 @@
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="7">
   <r>
     <d v="2017-01-01T00:00:00"/>
-    <s v="Mom"/>
+    <x v="0"/>
     <s v="Fuel"/>
     <n v="74"/>
   </r>
   <r>
     <d v="2017-01-15T00:00:00"/>
-    <s v="Mom"/>
+    <x v="0"/>
     <s v="Food"/>
     <n v="235"/>
   </r>
   <r>
     <d v="2017-01-17T00:00:00"/>
-    <s v="Dad"/>
+    <x v="1"/>
     <s v="Sports"/>
     <n v="20"/>
   </r>
   <r>
     <d v="2017-01-21T00:00:00"/>
-    <s v="Kelly"/>
+    <x v="2"/>
     <s v="Books"/>
     <n v="125"/>
   </r>
   <r>
     <d v="2017-02-02T00:00:00"/>
-    <s v="Mom"/>
+    <x v="0"/>
     <s v="Food"/>
     <n v="235"/>
   </r>
   <r>
     <d v="2017-02-20T00:00:00"/>
-    <s v="Kelly"/>
+    <x v="2"/>
     <s v="Music"/>
     <n v="20"/>
   </r>
   <r>
     <d v="2017-02-25T00:00:00"/>
-    <s v="Kelly"/>
+    <x v="2"/>
     <s v="Tickets"/>
     <n v="125"/>
   </r>
@@ -32576,20 +32652,181 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000000000000}" name="PivotTable1" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="H10:I14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{37D5C5E0-D246-FD4E-A350-D9F9DBEDB65F}" name="PivotTable3" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Buyers">
+  <location ref="M7:T12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
-    <pivotField compact="0" numFmtId="16" outline="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
       <items count="4">
         <item x="1"/>
+        <item x="2"/>
         <item x="0"/>
-        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" numFmtId="44" outline="0" showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="7">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="5" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="3" baseField="0" baseItem="0" numFmtId="5"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0B00-000000000000}" name="PivotTable11" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="H10:I14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField compact="0" numFmtId="16" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" numFmtId="44" outline="0" subtotalTop="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="3" baseField="0" baseItem="0" numFmtId="5"/>
+  </dataFields>
+  <formats count="4">
+    <format dxfId="0">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="1">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="2">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="3">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" altTextSummary="PivotTable with row field conditions that breaks down the value field" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0C00-000000000000}" name="PivotTable12" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="H10:I14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField compact="0" numFmtId="16" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" numFmtId="44" outline="0" subtotalTop="0" showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="1"/>
@@ -32615,21 +32852,17 @@
     <dataField name="Sum of Amount" fld="3" baseField="0" baseItem="0" numFmtId="5"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="112">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="1" count="0" selected="0"/>
-        </references>
-      </pivotArea>
+    <format dxfId="31">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="111">
+    <format dxfId="30">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" altTextSummary="Simple PivotTable summarizing the data contained in Expenses1 table" hideValuesRow="1"/>
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" altTextSummary="PivotTable with a Buyer row field that breaks down the Amount values in Expenses12 table and generates the Sum of Amounts field values" hideValuesRow="1"/>
     </ext>
     <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
       <xpdl:pivotTableDefinition16/>
@@ -32638,8 +32871,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0F00-000000000000}" name="PivotTable15" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0F00-000000000000}" name="PivotTable15" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="E12:E13" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="4">
     <pivotField numFmtId="164" subtotalTop="0" showAll="0"/>
@@ -32657,7 +32890,7 @@
     <dataField name="Sum of Amount" fld="3" baseField="0" baseItem="0" numFmtId="5"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="10">
+    <format dxfId="17">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -32673,8 +32906,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-1000-000000000000}" name="PivotTable16" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-1000-000000000000}" name="PivotTable16" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="E12:E13" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="4">
     <pivotField numFmtId="164" subtotalTop="0" showAll="0"/>
@@ -32692,7 +32925,7 @@
     <dataField name="Sum of Amount" fld="3" baseField="0" baseItem="0" numFmtId="5"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="9">
+    <format dxfId="16">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -32708,8 +32941,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-1100-000000000000}" name="PivotTable17" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-1100-000000000000}" name="PivotTable17" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="D12:E16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField numFmtId="164" subtotalTop="0" showAll="0"/>
@@ -32758,7 +32991,7 @@
     <dataField name="Sum of Amount" fld="3" baseField="0" baseItem="0" numFmtId="5"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="8">
+    <format dxfId="15">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -32774,8 +33007,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-1200-000000000000}" name="PivotTable Area" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-1200-000000000000}" name="PivotTable Area" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="H14:H15" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="5">
     <pivotField compact="0" numFmtId="16" outline="0" subtotalTop="0" showAll="0">
@@ -33192,10 +33425,10 @@
     <dataField name="Sum of Amount" fld="3" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="7">
+    <format dxfId="14">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="13">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -33212,7 +33445,154 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable2" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000000000000}" name="PivotTable1" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="H10:I14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField compact="0" numFmtId="16" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" numFmtId="44" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="3" baseField="0" baseItem="0" numFmtId="5"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="107">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0" selected="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="106">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" altTextSummary="Simple PivotTable summarizing the data contained in Expenses1 table" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{74FE9A45-7C37-1241-A72F-6B4B3EFE366D}" name="PivotTable4" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="N9:R17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="5" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="3" baseField="0" baseItem="0" numFmtId="5"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable2" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="G10:K18" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField compact="0" numFmtId="16" outline="0" subtotalTop="0" showAll="0"/>
@@ -33284,7 +33664,7 @@
     <dataField name="Sum of Amount" fld="3" baseField="2" baseItem="0" numFmtId="5"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="104">
+    <format dxfId="99">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -33300,8 +33680,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable3" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable3" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="G10:K18" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField numFmtId="16" subtotalTop="0" showAll="0"/>
@@ -33373,7 +33753,7 @@
     <dataField name="Sum of Amount" fld="3" baseField="0" baseItem="0" numFmtId="5"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="97">
+    <format dxfId="92">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -33436,17 +33816,38 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0700-000000000000}" name="PivotTable7" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="H10:H11" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0700-000000000000}" name="PivotTable7" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="H10:I14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField numFmtId="16" subtotalTop="0" showAll="0"/>
-    <pivotField subtotalTop="0" showAll="0"/>
+    <pivotField axis="axisRow" subtotalTop="0" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField subtotalTop="0" showAll="0"/>
     <pivotField dataField="1" numFmtId="44" subtotalTop="0" showAll="0"/>
   </pivotFields>
-  <rowItems count="1">
-    <i/>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
   </rowItems>
   <colItems count="1">
     <i/>
@@ -33455,10 +33856,10 @@
     <dataField name="Sum of Amount" fld="3" baseField="0" baseItem="0" numFmtId="5"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="72">
+    <format dxfId="115">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="71">
+    <format dxfId="114">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -33474,17 +33875,50 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0800-000000000000}" name="PivotTable8" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="H11:H12" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0800-000000000000}" name="PivotTable8" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="H11:I18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField numFmtId="16" subtotalTop="0" showAll="0"/>
     <pivotField subtotalTop="0" showAll="0"/>
-    <pivotField subtotalTop="0" showAll="0"/>
+    <pivotField axis="axisRow" subtotalTop="0" showAll="0">
+      <items count="7">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField dataField="1" numFmtId="44" subtotalTop="0" showAll="0"/>
   </pivotFields>
-  <rowItems count="1">
-    <i/>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
   </rowItems>
   <colItems count="1">
     <i/>
@@ -33493,11 +33927,11 @@
     <dataField name="Sum of Amount" fld="3" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="64">
+    <format dxfId="67">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="0" showRowStripes="0" showColStripes="1" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" altTextSummary="Sum of Amount column from Expenses8 table illustrating how numeric values turn into field values in a PivotTable" hideValuesRow="1"/>
@@ -33509,8 +33943,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0900-000000000000}" name="PivotTable9" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0900-000000000000}" name="PivotTable9" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="H11:I15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField compact="0" numFmtId="16" outline="0" subtotalTop="0" showAll="0"/>
@@ -33559,19 +33993,19 @@
     <dataField name="Sum of Amount" fld="3" baseField="0" baseItem="0" numFmtId="5"/>
   </dataFields>
   <formats count="5">
-    <format dxfId="57">
+    <format dxfId="60">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="56">
+    <format dxfId="59">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="55">
+    <format dxfId="58">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="54">
+    <format dxfId="57">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="53">
+    <format dxfId="56">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -33587,8 +34021,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0A00-000000000000}" name="PivotTable10" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0A00-000000000000}" name="PivotTable10" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="H10:I17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField compact="0" numFmtId="16" outline="0" subtotalTop="0" showAll="0"/>
@@ -33646,22 +34080,22 @@
     <dataField name="Sum of Amount" fld="3" baseField="0" baseItem="0" numFmtId="5"/>
   </dataFields>
   <formats count="6">
+    <format dxfId="49">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="48">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="47">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
     <format dxfId="46">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
     <format dxfId="45">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
     <format dxfId="44">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="43">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="42">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="41">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -33677,136 +34111,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0B00-000000000000}" name="PivotTable11" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="H10:I14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="4">
-    <pivotField compact="0" numFmtId="16" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" numFmtId="44" outline="0" subtotalTop="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Amount" fld="3" baseField="0" baseItem="0" numFmtId="5"/>
-  </dataFields>
-  <formats count="4">
-    <format dxfId="34">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="33">
-      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="32">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="1" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="31">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" altTextSummary="PivotTable with row field conditions that breaks down the value field" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0C00-000000000000}" name="PivotTable12" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="H10:I14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="4">
-    <pivotField compact="0" numFmtId="16" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" numFmtId="44" outline="0" subtotalTop="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Amount" fld="3" baseField="0" baseItem="0" numFmtId="5"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="24">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="23">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" altTextSummary="PivotTable with a Buyer row field that breaks down the Amount values in Expenses12 table and generates the Sum of Amounts field values" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Expenses1" displayName="Expenses1" ref="B10:E17" totalsRowShown="0" headerRowDxfId="110" tableBorderDxfId="109">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Expenses1" displayName="Expenses1" ref="B10:E17" totalsRowShown="0" headerRowDxfId="105" tableBorderDxfId="104">
   <autoFilter ref="B10:E17" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -33814,10 +34120,10 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Date" dataDxfId="108" dataCellStyle="Date"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Buyer" dataDxfId="107"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Type" dataDxfId="106"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Amount" dataDxfId="105" dataCellStyle="Currency"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Date" dataDxfId="103" dataCellStyle="Date"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Buyer" dataDxfId="102"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Type" dataDxfId="101"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Amount" dataDxfId="100" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -33829,7 +34135,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Expenses10" displayName="Expenses10" ref="B10:E17" totalsRowShown="0" headerRowDxfId="40" tableBorderDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Expenses10" displayName="Expenses10" ref="B10:E17" totalsRowShown="0" headerRowDxfId="43" tableBorderDxfId="42">
   <autoFilter ref="B10:E17" xr:uid="{00000000-0009-0000-0100-00000A000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -33837,10 +34143,10 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="Date" dataDxfId="38"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="Buyer" dataDxfId="37"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="Type" dataDxfId="36"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="Amount" dataDxfId="35"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="Date" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="Buyer" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="Type" dataDxfId="39"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="Amount" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -33852,7 +34158,7 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{00000000-000C-0000-FFFF-FFFF0A000000}" name="Expenses11" displayName="Expenses11" ref="B10:E17" totalsRowShown="0" headerRowDxfId="30" tableBorderDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{00000000-000C-0000-FFFF-FFFF0A000000}" name="Expenses11" displayName="Expenses11" ref="B10:E17" totalsRowShown="0" headerRowDxfId="37" tableBorderDxfId="36">
   <autoFilter ref="B10:E17" xr:uid="{00000000-0009-0000-0100-00000B000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -33860,10 +34166,10 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0A00-000001000000}" name="Date" dataDxfId="28" dataCellStyle="Date"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="Buyer" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0A00-000003000000}" name="Type" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0A00-000004000000}" name="Amount" dataDxfId="25" dataCellStyle="Currency"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0A00-000001000000}" name="Date" dataDxfId="35" dataCellStyle="Date"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="Buyer" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0A00-000003000000}" name="Type" dataDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0A00-000004000000}" name="Amount" dataDxfId="32" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -33875,7 +34181,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{00000000-000C-0000-FFFF-FFFF0B000000}" name="Expenses12" displayName="Expenses12" ref="B10:E17" totalsRowShown="0" headerRowDxfId="22" tableBorderDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{00000000-000C-0000-FFFF-FFFF0B000000}" name="Expenses12" displayName="Expenses12" ref="B10:E17" totalsRowShown="0" headerRowDxfId="29" tableBorderDxfId="28">
   <autoFilter ref="B10:E17" xr:uid="{00000000-0009-0000-0100-00000C000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -33883,10 +34189,10 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name="Date" dataDxfId="20" dataCellStyle="Date"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0B00-000002000000}" name="Buyer" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0B00-000003000000}" name="Type" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0B00-000004000000}" name="Amount" dataDxfId="17" dataCellStyle="Currency"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name="Date" dataDxfId="27" dataCellStyle="Date"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0B00-000002000000}" name="Buyer" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0B00-000003000000}" name="Type" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0B00-000004000000}" name="Amount" dataDxfId="24" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -33898,7 +34204,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{00000000-000C-0000-FFFF-FFFF0C000000}" name="Expenses13" displayName="Expenses13" ref="C14:F21" totalsRowShown="0" headerRowDxfId="16" tableBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{00000000-000C-0000-FFFF-FFFF0C000000}" name="Expenses13" displayName="Expenses13" ref="C14:F21" totalsRowShown="0" headerRowDxfId="23" tableBorderDxfId="22">
   <autoFilter ref="C14:F21" xr:uid="{00000000-0009-0000-0100-00000D000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -33906,10 +34212,10 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0C00-000001000000}" name="Date" dataDxfId="14" dataCellStyle="Date"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0C00-000002000000}" name="Buyer" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0C00-000003000000}" name="Type" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0C00-000004000000}" name="Amount" dataDxfId="11" dataCellStyle="Currency"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0C00-000001000000}" name="Date" dataDxfId="21" dataCellStyle="Date"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0C00-000002000000}" name="Buyer" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0C00-000003000000}" name="Type" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0C00-000004000000}" name="Amount" dataDxfId="18" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -33921,7 +34227,7 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{00000000-000C-0000-FFFF-FFFF0D000000}" name="Expenses18" displayName="Expenses18" ref="B14:E21" totalsRowShown="0" headerRowDxfId="5" tableBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{00000000-000C-0000-FFFF-FFFF0D000000}" name="Expenses18" displayName="Expenses18" ref="B14:E21" totalsRowShown="0" headerRowDxfId="12" tableBorderDxfId="11">
   <autoFilter ref="B14:E21" xr:uid="{00000000-0009-0000-0100-00000E000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -33929,10 +34235,10 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0D00-000001000000}" name="Date" dataDxfId="3" dataCellStyle="Date"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0D00-000002000000}" name="Buyer" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0D00-000003000000}" name="Type" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0D00-000004000000}" name="Amount" dataDxfId="0" dataCellStyle="Currency"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0D00-000001000000}" name="Date" dataDxfId="10" dataCellStyle="Date"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0D00-000002000000}" name="Buyer" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0D00-000003000000}" name="Type" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0D00-000004000000}" name="Amount" dataDxfId="7" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -33944,7 +34250,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Expenses2" displayName="Expenses2" ref="B10:E17" totalsRowShown="0" headerRowDxfId="103" tableBorderDxfId="102">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Expenses2" displayName="Expenses2" ref="B10:E17" totalsRowShown="0" headerRowDxfId="98" tableBorderDxfId="97">
   <autoFilter ref="B10:E17" xr:uid="{00000000-0009-0000-0100-000002000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -33952,10 +34258,10 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Date" dataDxfId="101" dataCellStyle="Date"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Buyer" dataDxfId="100"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Type" dataDxfId="99"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Amount" dataDxfId="98" dataCellStyle="Currency"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Date" dataDxfId="96" dataCellStyle="Date"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Buyer" dataDxfId="95"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Type" dataDxfId="94"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Amount" dataDxfId="93" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -33967,7 +34273,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Expenses3" displayName="Expenses3" ref="B10:E17" totalsRowShown="0" headerRowDxfId="96" tableBorderDxfId="95">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Expenses3" displayName="Expenses3" ref="B10:E17" totalsRowShown="0" headerRowDxfId="91" tableBorderDxfId="90">
   <autoFilter ref="B10:E17" xr:uid="{00000000-0009-0000-0100-000003000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -33975,10 +34281,10 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Date" dataDxfId="94" dataCellStyle="Date"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Buyer" dataDxfId="93"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Type" dataDxfId="92"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Amount" dataDxfId="91" dataCellStyle="Currency"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Date" dataDxfId="89" dataCellStyle="Date"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Buyer" dataDxfId="88"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Type" dataDxfId="87"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Amount" dataDxfId="86" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -33990,7 +34296,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Expenses4" displayName="Expenses4" ref="B10:E17" totalsRowShown="0" headerRowDxfId="90" tableBorderDxfId="89">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Expenses4" displayName="Expenses4" ref="B10:E17" totalsRowShown="0" headerRowDxfId="85" tableBorderDxfId="84">
   <autoFilter ref="B10:E17" xr:uid="{00000000-0009-0000-0100-000004000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -33998,10 +34304,10 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Date" dataDxfId="88" dataCellStyle="Date"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Buyer" dataDxfId="87"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Type" dataDxfId="86"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Amount" dataDxfId="85" dataCellStyle="Currency"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Date" dataDxfId="83" dataCellStyle="Date"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Buyer" dataDxfId="82"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Type" dataDxfId="81"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Amount" dataDxfId="80" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -34013,7 +34319,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Expenses5" displayName="Expenses5" ref="B10:E17" totalsRowShown="0" headerRowDxfId="84" tableBorderDxfId="83">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Expenses5" displayName="Expenses5" ref="B10:E17" totalsRowShown="0" headerRowDxfId="79" tableBorderDxfId="78">
   <autoFilter ref="B10:E17" xr:uid="{00000000-0009-0000-0100-000005000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -34021,10 +34327,10 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Date" dataDxfId="82" dataCellStyle="Date"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Buyer" dataDxfId="81"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Type" dataDxfId="80"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Amount" dataDxfId="79" dataCellStyle="Currency"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Date" dataDxfId="77" dataCellStyle="Date"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Buyer" dataDxfId="76"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Type" dataDxfId="75"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Amount" dataDxfId="74" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -34036,7 +34342,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Expenses6" displayName="Expenses6" ref="B10:E17" totalsRowShown="0" headerRowDxfId="78" tableBorderDxfId="77">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Expenses6" displayName="Expenses6" ref="B10:E17" totalsRowShown="0" headerRowDxfId="73" tableBorderDxfId="72">
   <autoFilter ref="B10:E17" xr:uid="{00000000-0009-0000-0100-000006000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -34044,10 +34350,10 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Date" dataDxfId="76" dataCellStyle="Date"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Buyer" dataDxfId="75"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Type" dataDxfId="74"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Amount" dataDxfId="73" dataCellStyle="Currency"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Date" dataDxfId="71" dataCellStyle="Date"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Buyer" dataDxfId="70"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Type" dataDxfId="69"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Amount" dataDxfId="68" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -34059,7 +34365,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Expenses7" displayName="Expenses7" ref="B10:E17" totalsRowShown="0" headerRowDxfId="70" tableBorderDxfId="69">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Expenses7" displayName="Expenses7" ref="B10:E17" totalsRowShown="0" headerRowDxfId="113" tableBorderDxfId="112">
   <autoFilter ref="B10:E17" xr:uid="{00000000-0009-0000-0100-000007000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -34067,10 +34373,10 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Date" dataDxfId="68"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Buyer" dataDxfId="67"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Type" dataDxfId="66"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Amount" dataDxfId="65"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Date" dataDxfId="111"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Buyer" dataDxfId="110"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Type" dataDxfId="109"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Amount" dataDxfId="108"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -34082,7 +34388,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Expenses8" displayName="Expenses8" ref="B11:E18" totalsRowShown="0" headerRowDxfId="63" tableBorderDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Expenses8" displayName="Expenses8" ref="B11:E18" totalsRowShown="0" headerRowDxfId="66" tableBorderDxfId="65">
   <autoFilter ref="B11:E18" xr:uid="{00000000-0009-0000-0100-000008000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -34090,10 +34396,10 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Date" dataDxfId="61" dataCellStyle="Date"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Buyer" dataDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Type" dataDxfId="59"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Amount" dataDxfId="58" dataCellStyle="Currency"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Date" dataDxfId="64" dataCellStyle="Date"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Buyer" dataDxfId="63"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Type" dataDxfId="62"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Amount" dataDxfId="61" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -34105,7 +34411,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Expenses9" displayName="Expenses9" ref="B11:E18" totalsRowShown="0" headerRowDxfId="52" tableBorderDxfId="51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Expenses9" displayName="Expenses9" ref="B11:E18" totalsRowShown="0" headerRowDxfId="55" tableBorderDxfId="54">
   <autoFilter ref="B11:E18" xr:uid="{00000000-0009-0000-0100-000009000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -34113,10 +34419,10 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="Date" dataDxfId="50" dataCellStyle="Date"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="Buyer" dataDxfId="49"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="Type" dataDxfId="48"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Amount" dataDxfId="47" dataCellStyle="Currency"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="Date" dataDxfId="53" dataCellStyle="Date"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="Buyer" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="Type" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Amount" dataDxfId="50" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -34428,34 +34734,34 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultColWidth="11.21875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="115.77734375" style="17" customWidth="1"/>
-    <col min="2" max="2" width="3.5546875" style="17" customWidth="1"/>
-    <col min="3" max="16384" width="11.21875" style="17"/>
+    <col min="1" max="1" width="115.83203125" style="17" customWidth="1"/>
+    <col min="2" max="2" width="3.5" style="17" customWidth="1"/>
+    <col min="3" max="16384" width="11.1640625" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="59.4" x14ac:dyDescent="1.2">
+    <row r="2" spans="1:1" ht="60" x14ac:dyDescent="0.75">
       <c r="A2" s="38" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="48" x14ac:dyDescent="0.3">
+      <c r="A3" s="39" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="44.4" x14ac:dyDescent="0.45">
-      <c r="A3" s="39" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="200.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" ht="200.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="19" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18"/>
     </row>
   </sheetData>
@@ -34471,36 +34777,36 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
-    <col min="7" max="7" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" style="2"/>
+    <col min="5" max="5" width="10.1640625" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B11" s="7" t="s">
         <v>3</v>
       </c>
@@ -34520,7 +34826,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B12" s="25">
         <v>42736</v>
       </c>
@@ -34540,7 +34846,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B13" s="26">
         <v>42750</v>
       </c>
@@ -34560,7 +34866,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B14" s="25">
         <v>42752</v>
       </c>
@@ -34580,7 +34886,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B15" s="26">
         <v>42756</v>
       </c>
@@ -34600,7 +34906,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B16" s="25">
         <v>42768</v>
       </c>
@@ -34614,7 +34920,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" s="26">
         <v>42786</v>
       </c>
@@ -34628,7 +34934,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B18" s="25">
         <v>42791</v>
       </c>
@@ -34660,36 +34966,36 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
-    <col min="7" max="7" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" style="2"/>
+    <col min="5" max="5" width="10.1640625" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B10" s="7" t="s">
         <v>3</v>
       </c>
@@ -34709,7 +35015,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B11" s="5">
         <v>42736</v>
       </c>
@@ -34729,7 +35035,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B12" s="6">
         <v>42750</v>
       </c>
@@ -34749,7 +35055,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B13" s="5">
         <v>42752</v>
       </c>
@@ -34769,7 +35075,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B14" s="6">
         <v>42756</v>
       </c>
@@ -34789,7 +35095,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B15" s="5">
         <v>42768</v>
       </c>
@@ -34809,7 +35115,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B16" s="6">
         <v>42786</v>
       </c>
@@ -34829,7 +35135,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B17" s="5">
         <v>42791</v>
       </c>
@@ -34867,36 +35173,36 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
-    <col min="7" max="7" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" style="2"/>
+    <col min="5" max="5" width="10.1640625" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B10" s="7" t="s">
         <v>3</v>
       </c>
@@ -34916,7 +35222,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B11" s="25">
         <v>42736</v>
       </c>
@@ -34936,7 +35242,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B12" s="26">
         <v>42750</v>
       </c>
@@ -34956,7 +35262,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B13" s="25">
         <v>42752</v>
       </c>
@@ -34976,7 +35282,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B14" s="26">
         <v>42756</v>
       </c>
@@ -34996,7 +35302,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B15" s="25">
         <v>42768</v>
       </c>
@@ -35010,7 +35316,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B16" s="26">
         <v>42786</v>
       </c>
@@ -35024,7 +35330,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" s="25">
         <v>42791</v>
       </c>
@@ -35056,41 +35362,41 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
-    <col min="7" max="7" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" style="2"/>
+    <col min="5" max="5" width="10.1640625" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B10" s="7" t="s">
         <v>3</v>
       </c>
@@ -35110,7 +35416,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B11" s="25">
         <v>42736</v>
       </c>
@@ -35130,7 +35436,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B12" s="26">
         <v>42750</v>
       </c>
@@ -35150,7 +35456,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B13" s="25">
         <v>42752</v>
       </c>
@@ -35170,7 +35476,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B14" s="26">
         <v>42756</v>
       </c>
@@ -35190,7 +35496,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B15" s="25">
         <v>42768</v>
       </c>
@@ -35204,7 +35510,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B16" s="26">
         <v>42786</v>
       </c>
@@ -35218,7 +35524,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" s="25">
         <v>42791</v>
       </c>
@@ -35250,43 +35556,43 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="2"/>
-    <col min="2" max="4" width="8.77734375" style="1"/>
-    <col min="5" max="6" width="10.21875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.83203125" style="2"/>
+    <col min="2" max="4" width="8.83203125" style="1"/>
+    <col min="5" max="6" width="10.1640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C14" s="7" t="s">
         <v>3</v>
       </c>
@@ -35300,7 +35606,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C15" s="25">
         <v>42736</v>
       </c>
@@ -35314,7 +35620,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C16" s="26">
         <v>42750</v>
       </c>
@@ -35328,7 +35634,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:6" x14ac:dyDescent="0.2">
       <c r="C17" s="25">
         <v>42752</v>
       </c>
@@ -35342,7 +35648,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:6" x14ac:dyDescent="0.2">
       <c r="C18" s="26">
         <v>42756</v>
       </c>
@@ -35356,7 +35662,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="19" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:6" x14ac:dyDescent="0.2">
       <c r="C19" s="25">
         <v>42768</v>
       </c>
@@ -35370,7 +35676,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="20" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:6" x14ac:dyDescent="0.2">
       <c r="C20" s="26">
         <v>42786</v>
       </c>
@@ -35384,7 +35690,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:6" x14ac:dyDescent="0.2">
       <c r="C21" s="25">
         <v>42791</v>
       </c>
@@ -35416,34 +35722,34 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="2"/>
-    <col min="2" max="4" width="8.77734375" style="1"/>
-    <col min="5" max="5" width="10.21875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.77734375" style="1"/>
-    <col min="7" max="7" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.83203125" style="2"/>
+    <col min="2" max="4" width="8.83203125" style="1"/>
+    <col min="5" max="5" width="10.1640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" style="1"/>
+    <col min="7" max="7" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="28" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="28" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -35463,46 +35769,46 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="2"/>
-    <col min="2" max="4" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.83203125" style="2"/>
+    <col min="2" max="4" width="8.83203125" style="1"/>
     <col min="5" max="5" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.77734375" style="1"/>
-    <col min="7" max="7" width="13.44140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.77734375" style="1"/>
+    <col min="6" max="6" width="8.83203125" style="1"/>
+    <col min="7" max="7" width="13.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="E12" t="s">
         <v>7</v>
       </c>
       <c r="F12"/>
       <c r="G12"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13"/>
@@ -35514,7 +35820,7 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B14" s="13"/>
       <c r="C14"/>
       <c r="D14"/>
@@ -35524,7 +35830,7 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B15" s="13"/>
       <c r="C15"/>
       <c r="D15"/>
@@ -35534,7 +35840,7 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B16" s="13"/>
       <c r="C16"/>
       <c r="D16"/>
@@ -35544,7 +35850,7 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B17" s="13"/>
       <c r="C17"/>
       <c r="D17"/>
@@ -35554,7 +35860,7 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B18" s="13"/>
       <c r="C18"/>
       <c r="D18"/>
@@ -35564,7 +35870,7 @@
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B19" s="13"/>
       <c r="C19"/>
       <c r="D19"/>
@@ -35574,7 +35880,7 @@
       <c r="H19"/>
       <c r="I19"/>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="13"/>
       <c r="C20"/>
       <c r="D20"/>
@@ -35584,70 +35890,70 @@
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.2">
       <c r="E21"/>
       <c r="F21"/>
       <c r="G21"/>
       <c r="H21"/>
       <c r="I21"/>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.2">
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22"/>
       <c r="H22"/>
       <c r="I22"/>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
       <c r="E23"/>
       <c r="F23"/>
       <c r="G23"/>
       <c r="H23"/>
       <c r="I23"/>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.2">
       <c r="E24"/>
       <c r="F24"/>
       <c r="G24"/>
       <c r="H24"/>
       <c r="I24"/>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.2">
       <c r="E25"/>
       <c r="F25"/>
       <c r="G25"/>
       <c r="H25"/>
       <c r="I25"/>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="E26"/>
       <c r="F26"/>
       <c r="G26"/>
       <c r="H26"/>
       <c r="I26"/>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.2">
       <c r="E27"/>
       <c r="F27"/>
       <c r="G27"/>
       <c r="H27"/>
       <c r="I27"/>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
       <c r="E28"/>
       <c r="F28"/>
       <c r="G28"/>
       <c r="H28"/>
       <c r="I28"/>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="E29"/>
       <c r="F29"/>
       <c r="G29"/>
       <c r="H29"/>
       <c r="I29"/>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.2">
       <c r="G30"/>
       <c r="H30"/>
       <c r="I30"/>
@@ -35667,44 +35973,44 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="2"/>
-    <col min="2" max="4" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.83203125" style="2"/>
+    <col min="2" max="4" width="8.83203125" style="1"/>
     <col min="5" max="5" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.77734375" style="1"/>
-    <col min="7" max="7" width="13.44140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.77734375" style="1"/>
+    <col min="6" max="6" width="8.83203125" style="1"/>
+    <col min="7" max="7" width="13.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="E12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13"/>
@@ -35714,7 +36020,7 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B14" s="13"/>
       <c r="C14"/>
       <c r="D14"/>
@@ -35722,7 +36028,7 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B15" s="13"/>
       <c r="C15"/>
       <c r="D15"/>
@@ -35731,7 +36037,7 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B16" s="13"/>
       <c r="C16"/>
       <c r="D16"/>
@@ -35740,7 +36046,7 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B17" s="13"/>
       <c r="C17"/>
       <c r="D17"/>
@@ -35749,7 +36055,7 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B18" s="13"/>
       <c r="C18"/>
       <c r="D18"/>
@@ -35758,7 +36064,7 @@
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B19" s="13"/>
       <c r="C19"/>
       <c r="D19"/>
@@ -35767,7 +36073,7 @@
       <c r="H19"/>
       <c r="I19"/>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="13"/>
       <c r="C20"/>
       <c r="D20"/>
@@ -35776,52 +36082,52 @@
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.2">
       <c r="G21"/>
       <c r="H21"/>
       <c r="I21"/>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.2">
       <c r="G22"/>
       <c r="H22"/>
       <c r="I22"/>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
       <c r="G23"/>
       <c r="H23"/>
       <c r="I23"/>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.2">
       <c r="G24"/>
       <c r="H24"/>
       <c r="I24"/>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.2">
       <c r="G25"/>
       <c r="H25"/>
       <c r="I25"/>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="G26"/>
       <c r="H26"/>
       <c r="I26"/>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.2">
       <c r="G27"/>
       <c r="H27"/>
       <c r="I27"/>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
       <c r="G28"/>
       <c r="H28"/>
       <c r="I28"/>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="G29"/>
       <c r="H29"/>
       <c r="I29"/>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.2">
       <c r="G30"/>
       <c r="H30"/>
       <c r="I30"/>
@@ -35841,46 +36147,46 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I31"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="2"/>
-    <col min="2" max="2" width="8.77734375" style="1"/>
-    <col min="3" max="3" width="8.77734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="8.83203125" style="1"/>
+    <col min="3" max="3" width="8.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="D12" s="8" t="s">
         <v>20</v>
       </c>
@@ -35888,7 +36194,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" s="12" t="s">
@@ -35900,7 +36206,7 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B14" s="13"/>
       <c r="C14"/>
       <c r="D14" s="12" t="s">
@@ -35912,7 +36218,7 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B15" s="13"/>
       <c r="C15"/>
       <c r="D15" s="12" t="s">
@@ -35925,7 +36231,7 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B16" s="13"/>
       <c r="C16"/>
       <c r="D16" s="12" t="s">
@@ -35938,7 +36244,7 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B17" s="13"/>
       <c r="C17"/>
       <c r="D17"/>
@@ -35947,7 +36253,7 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B18" s="13"/>
       <c r="C18"/>
       <c r="D18"/>
@@ -35956,7 +36262,7 @@
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B19" s="13"/>
       <c r="C19"/>
       <c r="D19"/>
@@ -35965,7 +36271,7 @@
       <c r="H19"/>
       <c r="I19"/>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="13"/>
       <c r="C20"/>
       <c r="D20"/>
@@ -35974,77 +36280,77 @@
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.2">
       <c r="D21"/>
       <c r="E21"/>
       <c r="G21"/>
       <c r="H21"/>
       <c r="I21"/>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.2">
       <c r="D22"/>
       <c r="E22"/>
       <c r="G22"/>
       <c r="H22"/>
       <c r="I22"/>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
       <c r="D23"/>
       <c r="E23"/>
       <c r="G23"/>
       <c r="H23"/>
       <c r="I23"/>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.2">
       <c r="D24"/>
       <c r="E24"/>
       <c r="G24"/>
       <c r="H24"/>
       <c r="I24"/>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.2">
       <c r="D25"/>
       <c r="E25"/>
       <c r="G25"/>
       <c r="H25"/>
       <c r="I25"/>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="D26"/>
       <c r="E26"/>
       <c r="G26"/>
       <c r="H26"/>
       <c r="I26"/>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.2">
       <c r="D27"/>
       <c r="E27"/>
       <c r="G27"/>
       <c r="H27"/>
       <c r="I27"/>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
       <c r="D28"/>
       <c r="E28"/>
       <c r="G28"/>
       <c r="H28"/>
       <c r="I28"/>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="D29"/>
       <c r="E29"/>
       <c r="G29"/>
       <c r="H29"/>
       <c r="I29"/>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.2">
       <c r="D30"/>
       <c r="E30"/>
       <c r="G30"/>
       <c r="H30"/>
       <c r="I30"/>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.2">
       <c r="D31"/>
       <c r="E31"/>
     </row>
@@ -36063,68 +36369,68 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
-    <col min="7" max="7" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" style="2"/>
+    <col min="5" max="5" width="10.1640625" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="H10" s="20"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="H11" s="20"/>
     </row>
-    <row r="12" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="19" x14ac:dyDescent="0.25">
       <c r="H12" s="21" t="str">
         <f>IF(AND($H$14="Buyer",$I$18=834),"Good job! You placed the fields correctly."," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B14" s="7" t="s">
         <v>3</v>
       </c>
@@ -36141,7 +36447,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B15" s="25">
         <v>42736</v>
       </c>
@@ -36158,7 +36464,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B16" s="26">
         <v>42750</v>
       </c>
@@ -36172,7 +36478,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" s="25">
         <v>42752</v>
       </c>
@@ -36186,7 +36492,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B18" s="26">
         <v>42756</v>
       </c>
@@ -36200,7 +36506,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B19" s="25">
         <v>42768</v>
       </c>
@@ -36214,7 +36520,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B20" s="26">
         <v>42786</v>
       </c>
@@ -36228,7 +36534,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B21" s="25">
         <v>42791</v>
       </c>
@@ -36262,42 +36568,107 @@
   <sheetPr codeName="Sheet3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:T24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="2" max="4" width="9.21875" style="1"/>
-    <col min="5" max="5" width="10.21875" style="1" customWidth="1"/>
-    <col min="6" max="7" width="9.21875" style="1"/>
-    <col min="8" max="8" width="10.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" style="2"/>
+    <col min="2" max="4" width="9.1640625" style="1"/>
+    <col min="5" max="5" width="10.1640625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="9.1640625" style="1"/>
+    <col min="8" max="8" width="10.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.21875" style="1"/>
+    <col min="10" max="12" width="9.1640625" style="1"/>
+    <col min="13" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="40"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="M7" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7"/>
+      <c r="P7"/>
+      <c r="Q7"/>
+      <c r="R7"/>
+      <c r="S7"/>
+      <c r="T7"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="M8" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="N8" t="s">
+        <v>14</v>
+      </c>
+      <c r="O8" t="s">
+        <v>11</v>
+      </c>
+      <c r="P8" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>16</v>
+      </c>
+      <c r="R8" t="s">
+        <v>12</v>
+      </c>
+      <c r="S8" t="s">
+        <v>17</v>
+      </c>
+      <c r="T8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="M9" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24">
+        <v>20</v>
+      </c>
+      <c r="S9" s="24"/>
+      <c r="T9" s="24">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B10" s="7" t="s">
         <v>3</v>
       </c>
@@ -36316,8 +36687,26 @@
       <c r="I10" t="s">
         <v>7</v>
       </c>
+      <c r="M10" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="N10" s="24">
+        <v>125</v>
+      </c>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24">
+        <v>20</v>
+      </c>
+      <c r="R10" s="24"/>
+      <c r="S10" s="24">
+        <v>125</v>
+      </c>
+      <c r="T10" s="24">
+        <v>270</v>
+      </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B11" s="25">
         <v>42736</v>
       </c>
@@ -36336,8 +36725,24 @@
       <c r="I11" s="24">
         <v>20</v>
       </c>
+      <c r="M11" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="N11" s="24"/>
+      <c r="O11" s="24">
+        <v>470</v>
+      </c>
+      <c r="P11" s="24">
+        <v>74</v>
+      </c>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="24"/>
+      <c r="S11" s="24"/>
+      <c r="T11" s="24">
+        <v>544</v>
+      </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B12" s="26">
         <v>42750</v>
       </c>
@@ -36356,8 +36761,32 @@
       <c r="I12" s="24">
         <v>544</v>
       </c>
+      <c r="M12" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="N12" s="24">
+        <v>125</v>
+      </c>
+      <c r="O12" s="24">
+        <v>470</v>
+      </c>
+      <c r="P12" s="24">
+        <v>74</v>
+      </c>
+      <c r="Q12" s="24">
+        <v>20</v>
+      </c>
+      <c r="R12" s="24">
+        <v>20</v>
+      </c>
+      <c r="S12" s="24">
+        <v>125</v>
+      </c>
+      <c r="T12" s="24">
+        <v>834</v>
+      </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B13" s="25">
         <v>42752</v>
       </c>
@@ -36376,8 +36805,13 @@
       <c r="I13" s="24">
         <v>270</v>
       </c>
+      <c r="M13"/>
+      <c r="N13"/>
+      <c r="O13"/>
+      <c r="P13"/>
+      <c r="Q13"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B14" s="26">
         <v>42756</v>
       </c>
@@ -36396,8 +36830,13 @@
       <c r="I14" s="24">
         <v>834</v>
       </c>
+      <c r="M14"/>
+      <c r="N14"/>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B15" s="25">
         <v>42768</v>
       </c>
@@ -36410,8 +36849,13 @@
       <c r="E15" s="22">
         <v>235</v>
       </c>
+      <c r="M15"/>
+      <c r="N15"/>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B16" s="26">
         <v>42786</v>
       </c>
@@ -36424,8 +36868,11 @@
       <c r="E16" s="23">
         <v>20</v>
       </c>
+      <c r="M16"/>
+      <c r="N16"/>
+      <c r="O16"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B17" s="25">
         <v>42791</v>
       </c>
@@ -36438,15 +36885,53 @@
       <c r="E17" s="22">
         <v>125</v>
       </c>
+      <c r="M17"/>
+      <c r="N17"/>
+      <c r="O17"/>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M18"/>
+      <c r="N18"/>
+      <c r="O18"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M19"/>
+      <c r="N19"/>
+      <c r="O19"/>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M20"/>
+      <c r="N20"/>
+      <c r="O20"/>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M21"/>
+      <c r="N21"/>
+      <c r="O21"/>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M22"/>
+      <c r="N22"/>
+      <c r="O22"/>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M23"/>
+      <c r="N23"/>
+      <c r="O23"/>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M24"/>
+      <c r="N24"/>
+      <c r="O24"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="53" fitToHeight="0" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
+  <pageSetup scale="53" fitToHeight="0" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
   <headerFooter differentFirst="1"/>
-  <drawing r:id="rId3"/>
+  <drawing r:id="rId4"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
@@ -36455,49 +36940,49 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="2"/>
-    <col min="2" max="4" width="8.77734375" style="1"/>
-    <col min="5" max="5" width="10.21875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.77734375" style="1"/>
-    <col min="7" max="7" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.83203125" style="2"/>
+    <col min="2" max="4" width="8.83203125" style="1"/>
+    <col min="5" max="5" width="10.1640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" style="1"/>
+    <col min="7" max="7" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -36513,51 +36998,51 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <sheetPr codeName="Sheet22"/>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
-    <col min="7" max="7" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5546875" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" style="2"/>
+    <col min="5" max="5" width="10.1640625" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B15" s="32" t="s">
         <v>3</v>
       </c>
@@ -36571,7 +37056,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B16" s="34">
         <v>42736</v>
       </c>
@@ -36585,7 +37070,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" s="35">
         <v>42750</v>
       </c>
@@ -36599,7 +37084,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B18" s="34">
         <v>42752</v>
       </c>
@@ -36613,7 +37098,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B19" s="35">
         <v>42756</v>
       </c>
@@ -36627,7 +37112,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B20" s="34">
         <v>42768</v>
       </c>
@@ -36641,7 +37126,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B21" s="35">
         <v>42786</v>
       </c>
@@ -36655,7 +37140,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B22" s="34">
         <v>42791</v>
       </c>
@@ -36682,42 +37167,42 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.55" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="2"/>
-    <col min="2" max="2" width="95.21875" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="95.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="14" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" s="14" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B2"/>
     </row>
-    <row r="3" spans="1:2" s="14" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" s="14" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B3"/>
     </row>
-    <row r="4" spans="1:2" s="15" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" s="15" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B4"/>
     </row>
-    <row r="5" spans="1:2" s="16" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" s="16" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B5"/>
     </row>
-    <row r="6" spans="1:2" s="16" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" s="16" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>61</v>
       </c>
@@ -36743,42 +37228,51 @@
   <sheetPr codeName="Sheet4">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:R18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" style="2"/>
+    <col min="5" max="5" width="10.1640625" customWidth="1"/>
     <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="N9" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B10" s="7" t="s">
         <v>3</v>
       </c>
@@ -36797,8 +37291,23 @@
       <c r="H10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="N10" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="O10" t="s">
+        <v>10</v>
+      </c>
+      <c r="P10" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B11" s="25">
         <v>42736</v>
       </c>
@@ -36826,8 +37335,19 @@
       <c r="K11" t="s">
         <v>15</v>
       </c>
+      <c r="N11" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O11" s="24"/>
+      <c r="P11" s="24">
+        <v>125</v>
+      </c>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="24">
+        <v>125</v>
+      </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B12" s="26">
         <v>42750</v>
       </c>
@@ -36851,8 +37371,19 @@
       <c r="K12" s="24">
         <v>125</v>
       </c>
+      <c r="N12" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24">
+        <v>470</v>
+      </c>
+      <c r="R12" s="24">
+        <v>470</v>
+      </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B13" s="25">
         <v>42752</v>
       </c>
@@ -36876,8 +37407,19 @@
       <c r="K13" s="24">
         <v>470</v>
       </c>
+      <c r="N13" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="O13" s="24"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24">
+        <v>74</v>
+      </c>
+      <c r="R13" s="24">
+        <v>74</v>
+      </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B14" s="26">
         <v>42756</v>
       </c>
@@ -36901,8 +37443,19 @@
       <c r="K14" s="24">
         <v>74</v>
       </c>
+      <c r="N14" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24">
+        <v>20</v>
+      </c>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24">
+        <v>20</v>
+      </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B15" s="25">
         <v>42768</v>
       </c>
@@ -36926,8 +37479,19 @@
       <c r="K15" s="24">
         <v>20</v>
       </c>
+      <c r="N15" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="O15" s="24">
+        <v>20</v>
+      </c>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="24">
+        <v>20</v>
+      </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B16" s="26">
         <v>42786</v>
       </c>
@@ -36951,8 +37515,19 @@
       <c r="K16" s="24">
         <v>20</v>
       </c>
+      <c r="N16" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24">
+        <v>125</v>
+      </c>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="24">
+        <v>125</v>
+      </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B17" s="25">
         <v>42791</v>
       </c>
@@ -36976,8 +37551,23 @@
       <c r="K17" s="24">
         <v>125</v>
       </c>
+      <c r="N17" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="O17" s="24">
+        <v>20</v>
+      </c>
+      <c r="P17" s="24">
+        <v>270</v>
+      </c>
+      <c r="Q17" s="24">
+        <v>544</v>
+      </c>
+      <c r="R17" s="24">
+        <v>834</v>
+      </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
       <c r="G18" t="s">
         <v>15</v>
       </c>
@@ -36997,11 +37587,11 @@
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="28" fitToHeight="0" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
+  <pageSetup scale="28" fitToHeight="0" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
   <headerFooter differentFirst="1"/>
-  <drawing r:id="rId3"/>
+  <drawing r:id="rId4"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
@@ -37012,39 +37602,39 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K18"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" style="2"/>
+    <col min="5" max="5" width="10.1640625" customWidth="1"/>
     <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>3</v>
       </c>
@@ -37064,7 +37654,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B11" s="25">
         <v>42736</v>
       </c>
@@ -37093,7 +37683,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B12" s="26">
         <v>42750</v>
       </c>
@@ -37118,7 +37708,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B13" s="25">
         <v>42752</v>
       </c>
@@ -37143,7 +37733,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B14" s="26">
         <v>42756</v>
       </c>
@@ -37168,7 +37758,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B15" s="25">
         <v>42768</v>
       </c>
@@ -37193,7 +37783,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B16" s="26">
         <v>42786</v>
       </c>
@@ -37218,7 +37808,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B17" s="25">
         <v>42791</v>
       </c>
@@ -37243,7 +37833,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
       <c r="G18" s="12" t="s">
         <v>15</v>
       </c>
@@ -37278,35 +37868,35 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
-    <col min="8" max="8" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" style="2"/>
+    <col min="5" max="5" width="10.1640625" customWidth="1"/>
+    <col min="8" max="8" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B10" s="7" t="s">
         <v>3</v>
       </c>
@@ -37320,7 +37910,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B11" s="25">
         <v>42736</v>
       </c>
@@ -37334,7 +37924,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B12" s="26">
         <v>42750</v>
       </c>
@@ -37348,7 +37938,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B13" s="25">
         <v>42752</v>
       </c>
@@ -37362,7 +37952,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B14" s="26">
         <v>42756</v>
       </c>
@@ -37376,7 +37966,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B15" s="25">
         <v>42768</v>
       </c>
@@ -37390,7 +37980,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B16" s="26">
         <v>42786</v>
       </c>
@@ -37404,7 +37994,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" s="25">
         <v>42791</v>
       </c>
@@ -37436,35 +38026,35 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
-    <col min="8" max="8" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" style="2"/>
+    <col min="5" max="5" width="10.1640625" customWidth="1"/>
+    <col min="8" max="8" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B10" s="7" t="s">
         <v>3</v>
       </c>
@@ -37478,7 +38068,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B11" s="25">
         <v>42736</v>
       </c>
@@ -37492,7 +38082,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B12" s="26">
         <v>42750</v>
       </c>
@@ -37506,7 +38096,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B13" s="25">
         <v>42752</v>
       </c>
@@ -37520,7 +38110,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B14" s="26">
         <v>42756</v>
       </c>
@@ -37534,7 +38124,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B15" s="25">
         <v>42768</v>
       </c>
@@ -37548,7 +38138,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B16" s="26">
         <v>42786</v>
       </c>
@@ -37562,7 +38152,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" s="25">
         <v>42791</v>
       </c>
@@ -37594,33 +38184,33 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
-    <col min="8" max="8" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" style="2"/>
+    <col min="5" max="5" width="10.1640625" customWidth="1"/>
+    <col min="8" max="8" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>3</v>
       </c>
@@ -37634,7 +38224,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B11" s="25">
         <v>42736</v>
       </c>
@@ -37648,7 +38238,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B12" s="26">
         <v>42750</v>
       </c>
@@ -37662,7 +38252,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B13" s="25">
         <v>42752</v>
       </c>
@@ -37676,7 +38266,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B14" s="26">
         <v>42756</v>
       </c>
@@ -37690,7 +38280,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B15" s="25">
         <v>42768</v>
       </c>
@@ -37704,7 +38294,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B16" s="26">
         <v>42786</v>
       </c>
@@ -37718,7 +38308,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" s="25">
         <v>42791</v>
       </c>
@@ -37749,40 +38339,40 @@
   <sheetPr codeName="Sheet9">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2" customWidth="1"/>
-    <col min="2" max="4" width="9.21875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.21875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.77734375" style="1"/>
-    <col min="7" max="7" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="9.1640625" style="2" customWidth="1"/>
+    <col min="2" max="4" width="9.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" style="1"/>
+    <col min="7" max="7" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B10" s="7" t="s">
         <v>3</v>
       </c>
@@ -37795,11 +38385,14 @@
       <c r="E10" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B11" s="5">
         <v>42736</v>
       </c>
@@ -37812,11 +38405,14 @@
       <c r="E11" s="10">
         <v>74</v>
       </c>
-      <c r="H11" s="24">
-        <v>834</v>
+      <c r="H11" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="24">
+        <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B12" s="6">
         <v>42750</v>
       </c>
@@ -37829,8 +38425,14 @@
       <c r="E12" s="11">
         <v>235</v>
       </c>
+      <c r="H12" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="24">
+        <v>270</v>
+      </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B13" s="5">
         <v>42752</v>
       </c>
@@ -37843,8 +38445,14 @@
       <c r="E13" s="10">
         <v>20</v>
       </c>
+      <c r="H13" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="24">
+        <v>544</v>
+      </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B14" s="6">
         <v>42756</v>
       </c>
@@ -37857,8 +38465,14 @@
       <c r="E14" s="11">
         <v>125</v>
       </c>
+      <c r="H14" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="24">
+        <v>834</v>
+      </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B15" s="5">
         <v>42768</v>
       </c>
@@ -37872,7 +38486,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B16" s="6">
         <v>42786</v>
       </c>
@@ -37886,7 +38500,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" s="5">
         <v>42791</v>
       </c>
@@ -37917,37 +38531,37 @@
   <sheetPr codeName="Sheet10">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
-    <col min="7" max="7" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" style="2"/>
+    <col min="5" max="5" width="10.1640625" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B11" s="7" t="s">
         <v>3</v>
       </c>
@@ -37960,11 +38574,14 @@
       <c r="E11" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B12" s="25">
         <v>42736</v>
       </c>
@@ -37977,11 +38594,14 @@
       <c r="E12" s="22">
         <v>74</v>
       </c>
-      <c r="H12" s="9">
-        <v>834</v>
+      <c r="H12" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="9">
+        <v>125</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B13" s="26">
         <v>42750</v>
       </c>
@@ -37994,8 +38614,14 @@
       <c r="E13" s="23">
         <v>235</v>
       </c>
+      <c r="H13" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" s="9">
+        <v>470</v>
+      </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B14" s="25">
         <v>42752</v>
       </c>
@@ -38008,8 +38634,14 @@
       <c r="E14" s="22">
         <v>20</v>
       </c>
+      <c r="H14" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" s="9">
+        <v>74</v>
+      </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B15" s="26">
         <v>42756</v>
       </c>
@@ -38022,8 +38654,14 @@
       <c r="E15" s="23">
         <v>125</v>
       </c>
+      <c r="H15" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="9">
+        <v>20</v>
+      </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B16" s="25">
         <v>42768</v>
       </c>
@@ -38036,8 +38674,14 @@
       <c r="E16" s="22">
         <v>235</v>
       </c>
+      <c r="H16" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" s="9">
+        <v>20</v>
+      </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B17" s="26">
         <v>42786</v>
       </c>
@@ -38050,8 +38694,14 @@
       <c r="E17" s="23">
         <v>20</v>
       </c>
+      <c r="H17" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" s="9">
+        <v>125</v>
+      </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B18" s="25">
         <v>42791</v>
       </c>
@@ -38063,6 +38713,12 @@
       </c>
       <c r="E18" s="22">
         <v>125</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="9">
+        <v>834</v>
       </c>
     </row>
   </sheetData>
@@ -38087,6 +38743,25 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1267097ee5f5874adfcc408041ae252e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="395891a93df65b14727750f2c06c306c" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -38362,25 +39037,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF2E394B-F75E-4244-8A70-E58274CB1B28}">
   <ds:schemaRefs>
@@ -38390,6 +39046,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FFC6C91-5C9C-41A3-B28D-6841DEE6CCE7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CD325BB-763E-4390-B60A-39D6BA05947C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -38408,16 +39076,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FFC6C91-5C9C-41A3-B28D-6841DEE6CCE7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>